--- a/rapporten/prijsrapport-2026-04-26.xlsx
+++ b/rapporten/prijsrapport-2026-04-26.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="131">
   <si>
     <t>Product</t>
   </si>
@@ -37,15 +37,21 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Omerta - Night Power Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379284</t>
   </si>
   <si>
-    <t>1840300</t>
+    <t>Bliksma Retail B.V.</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
+    <t>Omerta - Oud &amp; Class Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379307</t>
   </si>
   <si>
@@ -85,7 +91,7 @@
     <t>8719214751661</t>
   </si>
   <si>
-    <t>1738467</t>
+    <t>Glamorous Treats</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -94,7 +100,7 @@
     <t>5414666014427</t>
   </si>
   <si>
-    <t>1692530</t>
+    <t>Juwelium</t>
   </si>
   <si>
     <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
@@ -103,7 +109,7 @@
     <t>8719214757229</t>
   </si>
   <si>
-    <t>1556816</t>
+    <t>Dorsh</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -250,7 +256,7 @@
     <t>8721055493860</t>
   </si>
   <si>
-    <t>946246</t>
+    <t>Minimarkt W&amp;M</t>
   </si>
   <si>
     <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
@@ -373,109 +379,31 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>8721055494003</t>
-  </si>
-  <si>
-    <t>1762224</t>
-  </si>
-  <si>
-    <t>8721055494041</t>
-  </si>
-  <si>
-    <t>5414666009485</t>
-  </si>
-  <si>
-    <t>7640158817018</t>
-  </si>
-  <si>
-    <t>Omerta - Invasion Third Dimension - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658380368</t>
-  </si>
-  <si>
-    <t>8715658361466</t>
-  </si>
-  <si>
-    <t>8715658013006</t>
-  </si>
-  <si>
-    <t>8715658380238</t>
-  </si>
-  <si>
-    <t>7640158815021</t>
-  </si>
-  <si>
-    <t>8715658997436</t>
-  </si>
-  <si>
-    <t>8715658380702</t>
-  </si>
-  <si>
-    <t>8715658370147</t>
-  </si>
-  <si>
-    <t>8715658350637</t>
-  </si>
-  <si>
-    <t>8715658350361</t>
-  </si>
-  <si>
-    <t>8715658002796</t>
-  </si>
-  <si>
-    <t>8715658361619</t>
-  </si>
-  <si>
-    <t>8715658998471</t>
-  </si>
-  <si>
-    <t>8715658997764</t>
-  </si>
-  <si>
-    <t>8715658009054</t>
-  </si>
-  <si>
-    <t>7640158819180</t>
-  </si>
-  <si>
-    <t>8715658997702</t>
-  </si>
-  <si>
-    <t>Omerta - Rose Pure - Eau de Parfum - 100ml</t>
-  </si>
-  <si>
-    <t>8715658380696</t>
-  </si>
-  <si>
-    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658350705</t>
-  </si>
-  <si>
-    <t>Omerta - Faktz Select - Eau De Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658370215</t>
-  </si>
-  <si>
-    <t>8719992723812</t>
-  </si>
-  <si>
-    <t>8715658340287</t>
-  </si>
-  <si>
-    <t>NG Nightly Desire Eau de Toilette 100 ml</t>
-  </si>
-  <si>
-    <t>8718421831913</t>
-  </si>
-  <si>
-    <t>8721055493488</t>
-  </si>
-  <si>
-    <t>8721055493723</t>
+    <t>Dorall Quaint damesparfum eau de toilette 100 ml</t>
+  </si>
+  <si>
+    <t>6291012905399</t>
+  </si>
+  <si>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Omerta - Ma Merveilleuse - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658997443</t>
+  </si>
+  <si>
+    <t>Real Time Hunted For Men - eau de toilette voor heren - 100ML</t>
+  </si>
+  <si>
+    <t>8715658350521</t>
+  </si>
+  <si>
+    <t>Hello Kitty You're Cute Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
+    <t>8721055493303</t>
   </si>
 </sst>
 </file>
@@ -867,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -911,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>16.95</v>
@@ -923,21 +851,21 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>15.95</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>16.95</v>
@@ -949,21 +877,21 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>15.95</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>16.95</v>
@@ -975,21 +903,21 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
         <v>15.95</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>16.95</v>
@@ -1001,21 +929,21 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
         <v>15.95</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>16.95</v>
@@ -1027,21 +955,21 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>15.95</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>16.95</v>
@@ -1053,21 +981,21 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>15.95</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1">
         <v>16.89</v>
@@ -1079,21 +1007,21 @@
         <v>0.94</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>15.95</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1">
         <v>10.89</v>
@@ -1105,21 +1033,21 @@
         <v>0.9</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1">
         <v>9.99</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>9.95</v>
@@ -1131,21 +1059,21 @@
         <v>0.47</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1">
         <v>9.48</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1">
         <v>9.79</v>
@@ -1157,21 +1085,21 @@
         <v>0.3</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1">
         <v>9.49</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>9.79</v>
@@ -1183,21 +1111,21 @@
         <v>0.29</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
         <v>9.5</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1">
         <v>9.79</v>
@@ -1209,21 +1137,21 @@
         <v>0.29</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
         <v>9.5</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1">
         <v>9.79</v>
@@ -1235,21 +1163,21 @@
         <v>0.29</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
         <v>9.5</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
         <v>9.79</v>
@@ -1261,21 +1189,21 @@
         <v>0.29</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
         <v>9.5</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1">
         <v>9.79</v>
@@ -1287,21 +1215,21 @@
         <v>0.29</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
         <v>9.5</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1">
         <v>9.79</v>
@@ -1313,21 +1241,21 @@
         <v>0.29</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
         <v>9.5</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1">
         <v>9.79</v>
@@ -1339,21 +1267,21 @@
         <v>0.29</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="1">
         <v>9.5</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1">
         <v>9.79</v>
@@ -1365,21 +1293,21 @@
         <v>0.29</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
         <v>9.5</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1">
         <v>9.79</v>
@@ -1391,21 +1319,21 @@
         <v>0.29</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="1">
         <v>9.5</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1">
         <v>9.79</v>
@@ -1417,21 +1345,21 @@
         <v>0.29</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" s="1">
         <v>9.5</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1">
         <v>9.79</v>
@@ -1443,21 +1371,21 @@
         <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
         <v>9.5</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1">
         <v>9.79</v>
@@ -1469,21 +1397,21 @@
         <v>0.29</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" s="1">
         <v>9.5</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1">
         <v>9.79</v>
@@ -1495,21 +1423,21 @@
         <v>0.29</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1">
         <v>9.5</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1">
         <v>9.79</v>
@@ -1521,21 +1449,21 @@
         <v>0.29</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="1">
         <v>9.5</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1">
         <v>9.79</v>
@@ -1547,21 +1475,21 @@
         <v>0.29</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="1">
         <v>9.5</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1">
         <v>9.79</v>
@@ -1573,21 +1501,21 @@
         <v>0.29</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
         <v>9.5</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1">
         <v>9.79</v>
@@ -1599,21 +1527,21 @@
         <v>0.29</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="1">
         <v>9.5</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1">
         <v>9.79</v>
@@ -1625,21 +1553,21 @@
         <v>0.29</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
         <v>9.5</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
         <v>9.79</v>
@@ -1651,21 +1579,21 @@
         <v>0.29</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1">
         <v>9.5</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>9.79</v>
@@ -1677,21 +1605,21 @@
         <v>0.29</v>
       </c>
       <c r="F31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" s="1">
         <v>9.5</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1">
         <v>9.79</v>
@@ -1703,21 +1631,21 @@
         <v>0.29</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
         <v>9.5</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1">
         <v>9.79</v>
@@ -1729,21 +1657,21 @@
         <v>0.29</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
         <v>9.5</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>9.79</v>
@@ -1755,21 +1683,21 @@
         <v>0.29</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
         <v>9.5</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1">
         <v>5.25</v>
@@ -1781,21 +1709,21 @@
         <v>0.26</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G35" s="1">
         <v>4.99</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1">
         <v>5.25</v>
@@ -1807,21 +1735,21 @@
         <v>0.26</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G36" s="1">
         <v>4.99</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1">
         <v>5.25</v>
@@ -1833,21 +1761,21 @@
         <v>0.26</v>
       </c>
       <c r="F37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G37" s="1">
         <v>4.99</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1">
         <v>5.25</v>
@@ -1859,21 +1787,21 @@
         <v>0.26</v>
       </c>
       <c r="F38" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G38" s="1">
         <v>4.99</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1">
         <v>5.25</v>
@@ -1885,21 +1813,21 @@
         <v>0.26</v>
       </c>
       <c r="F39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G39" s="1">
         <v>4.99</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1">
         <v>5.25</v>
@@ -1911,21 +1839,21 @@
         <v>0.26</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G40" s="1">
         <v>4.99</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
         <v>5.25</v>
@@ -1937,21 +1865,21 @@
         <v>0.26</v>
       </c>
       <c r="F41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G41" s="1">
         <v>4.99</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1">
         <v>5.25</v>
@@ -1963,21 +1891,21 @@
         <v>0.26</v>
       </c>
       <c r="F42" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G42" s="1">
         <v>4.99</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1">
         <v>5.25</v>
@@ -1989,21 +1917,21 @@
         <v>0.26</v>
       </c>
       <c r="F43" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G43" s="1">
         <v>4.99</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1">
         <v>5.25</v>
@@ -2015,21 +1943,21 @@
         <v>0.26</v>
       </c>
       <c r="F44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G44" s="1">
         <v>4.99</v>
       </c>
       <c r="H44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1">
         <v>5.25</v>
@@ -2041,21 +1969,21 @@
         <v>0.26</v>
       </c>
       <c r="F45" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G45" s="1">
         <v>4.99</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1">
         <v>5.25</v>
@@ -2067,21 +1995,21 @@
         <v>0.26</v>
       </c>
       <c r="F46" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G46" s="1">
         <v>4.99</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1">
         <v>5.25</v>
@@ -2093,21 +2021,21 @@
         <v>0.26</v>
       </c>
       <c r="F47" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G47" s="1">
         <v>4.99</v>
       </c>
       <c r="H47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1">
         <v>5.25</v>
@@ -2119,21 +2047,21 @@
         <v>0.26</v>
       </c>
       <c r="F48" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G48" s="1">
         <v>4.99</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1">
         <v>5.25</v>
@@ -2145,21 +2073,21 @@
         <v>0.26</v>
       </c>
       <c r="F49" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G49" s="1">
         <v>4.99</v>
       </c>
       <c r="H49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1">
         <v>5.25</v>
@@ -2171,21 +2099,21 @@
         <v>0.26</v>
       </c>
       <c r="F50" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G50" s="1">
         <v>4.99</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1">
         <v>5.25</v>
@@ -2197,21 +2125,21 @@
         <v>0.26</v>
       </c>
       <c r="F51" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G51" s="1">
         <v>4.99</v>
       </c>
       <c r="H51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1">
         <v>5.25</v>
@@ -2223,21 +2151,21 @@
         <v>0.26</v>
       </c>
       <c r="F52" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G52" s="1">
         <v>4.99</v>
       </c>
       <c r="H52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C53" s="1">
         <v>5.25</v>
@@ -2249,21 +2177,21 @@
         <v>0.26</v>
       </c>
       <c r="F53" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G53" s="1">
         <v>4.99</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1">
         <v>5.25</v>
@@ -2275,21 +2203,21 @@
         <v>0.26</v>
       </c>
       <c r="F54" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G54" s="1">
         <v>4.99</v>
       </c>
       <c r="H54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1">
         <v>5.25</v>
@@ -2301,767 +2229,117 @@
         <v>0.26</v>
       </c>
       <c r="F55" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G55" s="1">
         <v>4.99</v>
       </c>
       <c r="H55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C56" s="1">
-        <v>15.52</v>
+        <v>14.75</v>
       </c>
       <c r="D56" s="1">
-        <v>15.32</v>
+        <v>14.62</v>
       </c>
       <c r="E56" s="1">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G56" s="1">
-        <v>15.32</v>
+        <v>14.62</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C57" s="1">
-        <v>15.52</v>
+        <v>14.75</v>
       </c>
       <c r="D57" s="1">
-        <v>15.32</v>
+        <v>14.65</v>
       </c>
       <c r="E57" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F57" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G57" s="1">
-        <v>15.32</v>
+        <v>14.65</v>
       </c>
       <c r="H57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C58" s="1">
-        <v>15.52</v>
+        <v>12.89</v>
       </c>
       <c r="D58" s="1">
-        <v>15.32</v>
+        <v>12.85</v>
       </c>
       <c r="E58" s="1">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F58" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G58" s="1">
-        <v>15.32</v>
+        <v>12.85</v>
       </c>
       <c r="H58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="1">
+        <v>11.51</v>
+      </c>
+      <c r="D59" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F59" t="s">
         <v>124</v>
       </c>
-      <c r="B59" t="s">
-        <v>124</v>
-      </c>
-      <c r="C59" s="1">
-        <v>16.19</v>
-      </c>
-      <c r="D59" s="1">
-        <v>16.01</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="F59" t="s">
-        <v>121</v>
-      </c>
       <c r="G59" s="1">
-        <v>16.01</v>
+        <v>11.5</v>
       </c>
       <c r="H59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" t="s">
-        <v>126</v>
-      </c>
-      <c r="C60" s="1">
-        <v>14.79</v>
-      </c>
-      <c r="D60" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0.14</v>
-      </c>
-      <c r="F60" t="s">
-        <v>121</v>
-      </c>
-      <c r="G60" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" t="s">
-        <v>127</v>
-      </c>
-      <c r="C61" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D61" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>121</v>
-      </c>
-      <c r="G61" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H61" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>128</v>
-      </c>
-      <c r="B62" t="s">
-        <v>128</v>
-      </c>
-      <c r="C62" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D62" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>121</v>
-      </c>
-      <c r="G62" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>129</v>
-      </c>
-      <c r="B63" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D63" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F63" t="s">
-        <v>121</v>
-      </c>
-      <c r="G63" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" t="s">
-        <v>130</v>
-      </c>
-      <c r="C64" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D64" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>121</v>
-      </c>
-      <c r="G64" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>131</v>
-      </c>
-      <c r="B65" t="s">
-        <v>131</v>
-      </c>
-      <c r="C65" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D65" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F65" t="s">
-        <v>121</v>
-      </c>
-      <c r="G65" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" t="s">
-        <v>132</v>
-      </c>
-      <c r="C66" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D66" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F66" t="s">
-        <v>121</v>
-      </c>
-      <c r="G66" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D67" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F67" t="s">
-        <v>121</v>
-      </c>
-      <c r="G67" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>134</v>
-      </c>
-      <c r="B68" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D68" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F68" t="s">
-        <v>121</v>
-      </c>
-      <c r="G68" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" t="s">
-        <v>135</v>
-      </c>
-      <c r="C69" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D69" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F69" t="s">
-        <v>121</v>
-      </c>
-      <c r="G69" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H69" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D70" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F70" t="s">
-        <v>121</v>
-      </c>
-      <c r="G70" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" t="s">
-        <v>137</v>
-      </c>
-      <c r="C71" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D71" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F71" t="s">
-        <v>121</v>
-      </c>
-      <c r="G71" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H71" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>138</v>
-      </c>
-      <c r="B72" t="s">
-        <v>138</v>
-      </c>
-      <c r="C72" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D72" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F72" t="s">
-        <v>121</v>
-      </c>
-      <c r="G72" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H72" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>139</v>
-      </c>
-      <c r="B73" t="s">
-        <v>139</v>
-      </c>
-      <c r="C73" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D73" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F73" t="s">
-        <v>121</v>
-      </c>
-      <c r="G73" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H73" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>140</v>
-      </c>
-      <c r="B74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C74" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D74" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F74" t="s">
-        <v>121</v>
-      </c>
-      <c r="G74" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H74" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>141</v>
-      </c>
-      <c r="B75" t="s">
-        <v>141</v>
-      </c>
-      <c r="C75" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D75" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F75" t="s">
-        <v>121</v>
-      </c>
-      <c r="G75" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H75" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>142</v>
-      </c>
-      <c r="B76" t="s">
-        <v>142</v>
-      </c>
-      <c r="C76" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D76" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F76" t="s">
-        <v>121</v>
-      </c>
-      <c r="G76" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H76" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>143</v>
-      </c>
-      <c r="B77" t="s">
-        <v>144</v>
-      </c>
-      <c r="C77" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D77" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E77" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F77" t="s">
-        <v>121</v>
-      </c>
-      <c r="G77" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H77" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>145</v>
-      </c>
-      <c r="B78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D78" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F78" t="s">
-        <v>121</v>
-      </c>
-      <c r="G78" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H78" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>147</v>
-      </c>
-      <c r="B79" t="s">
-        <v>148</v>
-      </c>
-      <c r="C79" s="1">
-        <v>14.75</v>
-      </c>
-      <c r="D79" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F79" t="s">
-        <v>121</v>
-      </c>
-      <c r="G79" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="H79" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>149</v>
-      </c>
-      <c r="B80" t="s">
-        <v>149</v>
-      </c>
-      <c r="C80" s="1">
-        <v>14.99</v>
-      </c>
-      <c r="D80" s="1">
-        <v>14.93</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="F80" t="s">
-        <v>121</v>
-      </c>
-      <c r="G80" s="1">
-        <v>14.93</v>
-      </c>
-      <c r="H80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>150</v>
-      </c>
-      <c r="B81" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" s="1">
-        <v>13.25</v>
-      </c>
-      <c r="D81" s="1">
-        <v>13.21</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F81" t="s">
-        <v>121</v>
-      </c>
-      <c r="G81" s="1">
-        <v>13.21</v>
-      </c>
-      <c r="H81" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>151</v>
-      </c>
-      <c r="B82" t="s">
-        <v>152</v>
-      </c>
-      <c r="C82" s="1">
-        <v>12.89</v>
-      </c>
-      <c r="D82" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F82" t="s">
-        <v>121</v>
-      </c>
-      <c r="G82" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="H82" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>153</v>
-      </c>
-      <c r="B83" t="s">
-        <v>153</v>
-      </c>
-      <c r="C83" s="1">
-        <v>11.53</v>
-      </c>
-      <c r="D83" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="F83" t="s">
-        <v>121</v>
-      </c>
-      <c r="G83" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="H83" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84" t="s">
-        <v>154</v>
-      </c>
-      <c r="C84" s="1">
-        <v>12.39</v>
-      </c>
-      <c r="D84" s="1">
-        <v>12.37</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="F84" t="s">
-        <v>121</v>
-      </c>
-      <c r="G84" s="1">
-        <v>12.37</v>
-      </c>
-      <c r="H84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
